--- a/data/worldcup_0626_0623update.xlsx
+++ b/data/worldcup_0626_0623update.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -618,96 +618,104 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>How Deniz Undav became Germany’s World Cup 2026 supersub</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/how-deniz-undav-became-germanys-world-cup-2026-supersub</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denis Undav turns 30 on Sunday, July 19. A significant date for another reason – it's is the date of the 2026 World Cup Final which will be played at </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Germany defender Schlotterbeck out of World Cup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-22T12:47:20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cgk6rzd5g58o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nico Schlotterbeck made his international debut in March 2022  Germany defender Nico Schlotterbeck has been ruled out of the rest of the World Cup wit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>不虚此行！新军佛得角、库拉索、约旦、乌兹均取得世界杯首球</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-06-22 06:32</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956261</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2026年美加墨世界杯扩军至48支球队，佛得角、库拉索、约旦、乌兹别克斯坦成为了本届世界杯的四支新军。在佛得角队取得历史性首球后，本届世界杯的四支新军都已经取得进球，其中佛得角和库拉索还实现了拿一分的目标。
 佛得角世界杯首秀0-0逼平西班牙，就已经足够令人震惊，他们又在与乌拉圭的比赛中由凯文-皮纳</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>库拉索队医：不意外自己是本届世界杯唯一女队医</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-06-22 01:13</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955773.html</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>陈达毅盛赞鲁姆：非常了不起，是他让库拉索队继续留在世界杯</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:02</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955668.html</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eloy Room puts on a World Cup clinic: 15 saves and a perfect Sofascore Rating 10 in Curaçao’s 0-0 vs Ecuador</t>
+          <t>库拉索队医：不意外自己是本届世界杯唯一女队医</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-21T05:06:25</t>
+          <t>2026-06-22 01:13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/eloy-room-puts-on-a-world-cup-clinic-15-saves-and-a-perfect-sofascore-rating-10-in-curacaos-0-0-vs-ecuador</t>
+          <t>https://www.dongqiudi.com/articles/5955773.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -715,88 +723,80 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Meet the record-equalling keeper who helped Curacao make history</t>
+          <t>陈达毅盛赞鲁姆：非常了不起，是他让库拉索队继续留在世界杯</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-21T04:29:28</t>
+          <t>2026-06-22 00:02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cvg58z9gl34o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Impenetrable Room inspires Curacao to first World Cup point against Ecuador  As Ecuador forward Enner Valencia raced through on Curacao's goal inside </t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955668.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Impenetrable Room inspires Curacao to first World Cup point</t>
+          <t>Eloy Room puts on a World Cup clinic: 15 saves and a perfect Sofascore Rating 10 in Curaçao’s 0-0 vs Ecuador</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-21T03:14:41</t>
+          <t>2026-06-21T05:06:25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/videos/c3dyvklky1mo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Curacao goalkeeper Eloy Room equals the record for most saves in a World Cup match, as Dick Advocaat's side earn their first ever point in the tournam</t>
-        </is>
-      </c>
+          <t>https://www.sofascore.com/news/eloy-room-puts-on-a-world-cup-clinic-15-saves-and-a-perfect-sofascore-rating-10-in-curacaos-0-0-vs-ecuador</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ecuador 0-0 Curaçao Stats: Sensational Room Earns Blue Wave Their First World Cup Point</t>
+          <t>Meet the record-equalling keeper who helped Curacao make history</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-21T02:30:15</t>
+          <t>2026-06-21T04:29:28</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/ecuador-vs-curacao-stats-world-cup-2026/</t>
+          <t>https://www.bbc.com/sport/football/articles/cvg58z9gl34o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ecuador huffed and puffed but were unable to find a way past Curacao, with Eloy Room’s 15 saves earning them their first World Cup point. . Re-live th</t>
+          <t xml:space="preserve">Impenetrable Room inspires Curacao to first World Cup point against Ecuador  As Ecuador forward Enner Valencia raced through on Curacao's goal inside </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>From factory floor to World Cup star - Germany's super-sub Undav</t>
+          <t>Impenetrable Room inspires Curacao to first World Cup point</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -806,85 +806,93 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-21T00:22:07</t>
+          <t>2026-06-21T03:14:41</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c8r2pm4xrxro?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/sport/football/videos/c3dyvklky1mo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Undav's double wins it late on for Germany  It was not long ago that he was being publicly called out by manager Julian Nagelsmann - but Deniz Undav i</t>
+          <t>Curacao goalkeeper Eloy Room equals the record for most saves in a World Cup match, as Dick Advocaat's side earn their first ever point in the tournam</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>库拉索国家队官方发布社媒，晒出了球队夺得世界杯首分后的更衣室大合影。</t>
+          <t>Ecuador 0-0 Curaçao Stats: Sensational Room Earns Blue Wave Their First World Cup Point</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-21 18:53</t>
+          <t>2026-06-21T02:30:15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954377.html</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/ecuador-vs-curacao-stats-world-cup-2026/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ecuador huffed and puffed but were unable to find a way past Curacao, with Eloy Room’s 15 saves earning them their first World Cup point. . Re-live th</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>孤胆英雄！库拉索37岁门将鲁姆15次扑救，打破世界杯90分钟扑救纪录</t>
+          <t>From factory floor to World Cup star - Germany's super-sub Undav</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-21 09:57</t>
+          <t>2026-06-21T00:22:07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954091.html</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/c8r2pm4xrxro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Undav's double wins it late on for Germany  It was not long ago that he was being publicly called out by manager Julian Nagelsmann - but Deniz Undav i</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ecuador vs Curaçao: World Cup Group E starts to take shape in Kansas City</t>
+          <t>库拉索国家队官方发布社媒，晒出了球队夺得世界杯首分后的更衣室大合影。</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-20T13:00:00</t>
+          <t>2026-06-21 18:53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/ecuador-vs-curacao-world-cup-group-e-starts-to-take-shape-in-kansas-city</t>
+          <t>https://www.dongqiudi.com/articles/5954377.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -892,212 +900,285 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>孤胆英雄！库拉索37岁门将鲁姆15次扑救，打破世界杯90分钟扑救纪录</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:57</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954091.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ecuador vs Curaçao: World Cup Group E starts to take shape in Kansas City</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-20T13:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/ecuador-vs-curacao-world-cup-group-e-starts-to-take-shape-in-kansas-city</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Ecuador vs Curaçao Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2026-06-19T11:56:16</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/ecuador-vs-curacao-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Ecuador and Curaçao will be looking to keep their FIFA World Cup campaigns alive when they meet in Kansas City on Saturday.
 Curaçao will be hoping to</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Germany vs Ivory Coast Prediction: World Cup 2026 Match Preview</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-06-19T11:48:21</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/germany-vs-ivory-coast-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Can anyone maintain a 100% start in Group E? We look ahead to Saturday’s FIFA World Cup showdown in Toronto with our Germany vs Ivory Coast prediction</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>‘Gary, that’s my job’: Lineker makes ITV presenting cameo on World Cup coverage</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 21</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/2026/jun/20/gary-lineker-itv-presenting-cameo-world-cup-coverage</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Gary Lineker in familiar territory as he kicked off his ITV appearance with a light-hearted cameo as a presenter  Gary Lineker was back in familiar te</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Germany vs Ivory Coast Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-19T11:48:21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/germany-vs-ivory-coast-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Can anyone maintain a 100% start in Group E? We look ahead to Saturday’s FIFA World Cup showdown in Toronto with our Germany vs Ivory Coast prediction</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>‘Gary, that’s my job’: Lineker makes ITV presenting cameo on World Cup coverage</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 21</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/20/gary-lineker-itv-presenting-cameo-world-cup-coverage</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Gary Lineker in familiar territory as he kicked off his ITV appearance with a light-hearted cameo as a presenter  Gary Lineker was back in familiar te</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tuchel’s brash Britpop football is music to England ears before Ghana test</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/23/thomas-tuchel-britpop-football-england-world-cup-ghana</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Vinyl has baffled youngsters at the team’s hotel but spells of opening victory against Croatia showed side in the groove  I nside the foyer of the Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>E组积分榜：德国积6分锁定头名，厄瓜多尔仅1分陷入绝境</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-06-21 10:07</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5954148.html</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>How does qualification for the World Cup knockout stage work?</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-06-20T16:24:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Germany vs Côte d’Ivoire: Group E pregame report from Toronto</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-06-20T12:00:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/germany-vs-cote-divoire-group-e-pregame-report-from-toronto</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Germany meet Côte d’Ivoire in World Cup 2026 Group E at BMO Field. Form trends, key stats, players to watch, and decimal odds set up a compelling matc</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>E组积分榜：德国积6分锁定头名，厄瓜多尔仅1分陷入绝境</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-21 10:07</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954148.html</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Germany vs Côte d’Ivoire: Group E pregame report from Toronto</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-20T12:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/germany-vs-cote-divoire-group-e-pregame-report-from-toronto</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Germany meet Côte d’Ivoire in World Cup 2026 Group E at BMO Field. Form trends, key stats, players to watch, and decimal odds set up a compelling matc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>World Cup 2026: Routes to the final</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2026-06-19T12:00:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
         </is>
@@ -1114,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1383,25 +1464,106 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>How Deniz Undav became Germany’s World Cup 2026 supersub</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/how-deniz-undav-became-germanys-world-cup-2026-supersub</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denis Undav turns 30 on Sunday, July 19. A significant date for another reason – it's is the date of the 2026 World Cup Final which will be played at </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>How to watch Argentina vs Austria for FREE: Live stream details for Lionel Messi's record attempt at World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 15</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-argentina-vs-austria-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lionel Messi's hat-trick in Argentina's first match at World Cup 2026 took him level with German striker Miroslav Klose as the record scorer at men's </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Germany defender Schlotterbeck out of World Cup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-22T12:47:20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cgk6rzd5g58o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Nico Schlotterbeck made his international debut in March 2022  Germany defender Nico Schlotterbeck has been ruled out of the rest of the World Cup wit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>我们仨~土耳其62射厄瓜多尔39射不进球，比利时38射只进1乌龙</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-06-22 07:06</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956300</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>美加墨世界杯前两轮比赛，土耳其2连败出局，厄瓜多尔1平1负陷入绝境，比利时2连平浪费好签。
 土耳其两场比赛62脚射门，场均控球率75.5%，总预期进球3.53粒，结果0进球两连败小组出局。
@@ -1410,335 +1572,354 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>不虚此行！新军佛得角、库拉索、约旦、乌兹均取得世界杯首球</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2026-06-22 06:32</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956261</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>2026年美加墨世界杯扩军至48支球队，佛得角、库拉索、约旦、乌兹别克斯坦成为了本届世界杯的四支新军。在佛得角队取得历史性首球后，本届世界杯的四支新军都已经取得进球，其中佛得角和库拉索还实现了拿一分的目标。
 佛得角世界杯首秀0-0逼平西班牙，就已经足够令人震惊，他们又在与乌拉圭的比赛中由凯文-皮纳</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>世界杯开场25分钟进3球，西班牙是本世纪继德国之后第二队</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>dongqiudi_team</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2026-06-22 00:40</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/articles/5955747.html</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>2026-06-21T18:22:43</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
 The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Eloy Room puts on a World Cup clinic: 15 saves and a perfect Sofascore Rating 10 in Curaçao’s 0-0 vs Ecuador</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-06-21T05:06:25</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/eloy-room-puts-on-a-world-cup-clinic-15-saves-and-a-perfect-sofascore-rating-10-in-curacaos-0-0-vs-ecuador</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Meet the record-equalling keeper who helped Curacao make history</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-06-21T04:29:28</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cvg58z9gl34o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Impenetrable Room inspires Curacao to first World Cup point against Ecuador  As Ecuador forward Enner Valencia raced through on Curacao's goal inside </t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Ecuador 0-0 Curaçao Stats: Sensational Room Earns Blue Wave Their First World Cup Point</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-06-21T02:30:15</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/ecuador-vs-curacao-stats-world-cup-2026/</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Ecuador huffed and puffed but were unable to find a way past Curacao, with Eloy Room’s 15 saves earning them their first World Cup point. . Re-live th</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>From factory floor to World Cup star - Germany's super-sub Undav</t>
+          <t>Eloy Room puts on a World Cup clinic: 15 saves and a perfect Sofascore Rating 10 in Curaçao’s 0-0 vs Ecuador</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-21T00:22:07</t>
+          <t>2026-06-21T05:06:25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c8r2pm4xrxro?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Undav's double wins it late on for Germany  It was not long ago that he was being publicly called out by manager Julian Nagelsmann - but Deniz Undav i</t>
-        </is>
-      </c>
+          <t>https://www.sofascore.com/news/eloy-room-puts-on-a-world-cup-clinic-15-saves-and-a-perfect-sofascore-rating-10-in-curacaos-0-0-vs-ecuador</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>世界杯首次首发：国米前锋博尼vs德国数据一览</t>
+          <t>Meet the record-equalling keeper who helped Curacao make history</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-21 19:51</t>
+          <t>2026-06-21T04:29:28</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955176.html</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/cvg58z9gl34o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impenetrable Room inspires Curacao to first World Cup point against Ecuador  As Ecuador forward Enner Valencia raced through on Curacao's goal inside </t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>优势战绩，德国世界杯9战非洲队仅1负</t>
+          <t>Ecuador 0-0 Curaçao Stats: Sensational Room Earns Blue Wave Their First World Cup Point</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-21 06:32</t>
+          <t>2026-06-21T02:30:15</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953756.html</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/ecuador-vs-curacao-stats-world-cup-2026/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ecuador huffed and puffed but were unable to find a way past Curacao, with Eloy Room’s 15 saves earning them their first World Cup point. . Re-live th</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ecuador vs Curaçao: World Cup Group E starts to take shape in Kansas City</t>
+          <t>From factory floor to World Cup star - Germany's super-sub Undav</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-20T13:00:00</t>
+          <t>2026-06-21T00:22:07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/ecuador-vs-curacao-world-cup-group-e-starts-to-take-shape-in-kansas-city</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/c8r2pm4xrxro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Undav's double wins it late on for Germany  It was not long ago that he was being publicly called out by manager Julian Nagelsmann - but Deniz Undav i</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>世界杯首次首发：国米前锋博尼vs德国数据一览</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-21 19:51</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955176.html</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>优势战绩，德国世界杯9战非洲队仅1负</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-21 06:32</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953756.html</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ecuador vs Curaçao: World Cup Group E starts to take shape in Kansas City</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-20T13:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/ecuador-vs-curacao-world-cup-group-e-starts-to-take-shape-in-kansas-city</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Ecuador vs Curaçao Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2026-06-19T11:56:16</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/ecuador-vs-curacao-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Ecuador and Curaçao will be looking to keep their FIFA World Cup campaigns alive when they meet in Kansas City on Saturday.
 Curaçao will be hoping to</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Germany vs Ivory Coast Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2026-06-19T11:48:21</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/germany-vs-ivory-coast-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Can anyone maintain a 100% start in Group E? We look ahead to Saturday’s FIFA World Cup showdown in Toronto with our Germany vs Ivory Coast prediction</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>执教法国队取世界杯16胜，德尚与德国传奇教练舍恩并列最多</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959225&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>这场摸鱼，佛得角门将沃齐尼亚对阵乌拉圭没有完成扑救</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2026-06-22 08:14</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956388</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>佛得角2-2战平乌拉圭的比赛中，首轮表现亮眼的沃齐尼亚这回“美美隐身”了。
 本场比赛，乌拉圭全场只有2次射正，但都取得了进球，沃齐尼亚没能完成哪怕一次扑救。上轮对阵西班牙，沃齐尼亚7次扑救力保球门不失。
@@ -1748,28 +1929,28 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>逼平乌拉圭！佛得角FIFA排名上升4名，来到第63位</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2026-06-22 08:13</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956387</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>北京时间6月22日，佛得角在H组的第二轮小组赛中2-2逼平南美豪强乌拉圭，他们的FIFA排名也来到第63位。
 在本场逼平乌拉圭后，
@@ -1786,257 +1967,284 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>穆斯莱拉世界杯4次失误导致丢球，有统计以来所有门将最多</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2026-06-22 07:48</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956354</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>北京时间6月22日，在世界杯H组第二轮乌拉圭和佛得角的比赛中，现年40岁的穆斯莱拉第61分钟出现出击失误，随后被打空门得手并且将比分追平为2-2。
 根据Opta的统计，这是穆斯莱拉职业生涯至今在世界杯上第4次因失误导致本队丢球，他也就此超越了诺伊尔、施瓦泽以及代亚耶亚(均为3次)，成为自1966年有</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>穆勒评德国队失球：基米希给了迪奥曼德边路传中空间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-06-21 22:44</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955461.html</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>纳格尔斯曼：萨内在防守端非常积极，为基米希提供了很好支持</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-06-21 11:44</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5954309.html</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>诺伊尔世界杯连续8场丢球，自98年坎波斯以来门将第一人</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-06-21 05:26</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5953641.html</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>老登齐冲榜，C罗、魔笛、哲科、诺伊尔进入世界杯出场年龄榜前十</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-06-19 06:55</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5947861.html</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-    </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>‘Gary, that’s my job’: Lineker makes ITV presenting cameo on World Cup coverage</t>
+          <t>穆勒评德国队失球：基米希给了迪奥曼德边路传中空间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 21</t>
+          <t>2026-06-21 22:44</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/20/gary-lineker-itv-presenting-cameo-world-cup-coverage</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Gary Lineker in familiar territory as he kicked off his ITV appearance with a light-hearted cameo as a presenter  Gary Lineker was back in familiar te</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955461.html</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>纳格尔斯曼：萨内在防守端非常积极，为基米希提供了很好支持</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-21 11:44</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954309.html</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>诺伊尔世界杯连续8场丢球，自98年坎波斯以来门将第一人</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-21 05:26</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953641.html</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>老登齐冲榜，C罗、魔笛、哲科、诺伊尔进入世界杯出场年龄榜前十</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-19 06:55</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5947861.html</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>‘Gary, that’s my job’: Lineker makes ITV presenting cameo on World Cup coverage</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 21</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/20/gary-lineker-itv-presenting-cameo-world-cup-coverage</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Gary Lineker in familiar territory as he kicked off his ITV appearance with a light-hearted cameo as a presenter  Gary Lineker was back in familiar te</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Tuchel’s brash Britpop football is music to England ears before Ghana test</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 23</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/23/thomas-tuchel-britpop-football-england-world-cup-ghana</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Vinyl has baffled youngsters at the team’s hotel but spells of opening victory against Croatia showed side in the groove  I nside the foyer of the Eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>How does qualification for the World Cup knockout stage work?</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>2026-06-20T16:24:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Germany vs Côte d’Ivoire: Group E pregame report from Toronto</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>2026-06-20T12:00:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/germany-vs-cote-divoire-group-e-pregame-report-from-toronto</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Germany meet Côte d’Ivoire in World Cup 2026 Group E at BMO Field. Form trends, key stats, players to watch, and decimal odds set up a compelling matc</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>World Cup 2026: Routes to the final</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>2026-06-19T12:00:00</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
         </is>
@@ -2053,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2941,58 +3149,62 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>How Deniz Undav became Germany’s World Cup 2026 supersub</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/how-deniz-undav-became-germanys-world-cup-2026-supersub</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denis Undav turns 30 on Sunday, July 19. A significant date for another reason – it's is the date of the 2026 World Cup Final which will be played at </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Japan outclass Tunisia 4-0 in Group F: Ueda shines</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-06-21T08:06:08</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/japan-outclass-tunisia-4-0-in-group-f-ueda-shines</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-    </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tunisia vs Japan: Group F pregame at Estadio BBVA</t>
+          <t>Japan outclass Tunisia 4-0 in Group F: Ueda shines</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3002,71 +3214,119 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-20T15:00:00</t>
+          <t>2026-06-21T08:06:08</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/tunisia-vs-japan-group-f-pregame-at-estadio-bbva</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Tunisia face Japan in World Cup Group F at Estadio BBVA. See odds in decimal, H2H record, likely lineups, and Players to watch with Sofascore Rating.</t>
-        </is>
-      </c>
+          <t>https://www.sofascore.com/news/japan-outclass-tunisia-4-0-in-group-f-ueda-shines</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>World Cup 2026: Routes to the final</t>
+          <t>Tunisia vs Japan: Group F pregame at Estadio BBVA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-06-19T12:00:00</t>
+          <t>2026-06-20T15:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+          <t>https://www.sofascore.com/news/tunisia-vs-japan-group-f-pregame-at-estadio-bbva</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+          <t>Tunisia face Japan in World Cup Group F at Estadio BBVA. See odds in decimal, H2H record, likely lineups, and Players to watch with Sofascore Rating.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>World Cup 2026: Routes to the final</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-06-19T12:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Iran World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>11 hours ago</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/iran-world-cup-2026-fixtures-squad-analysis-june-21/</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Iran are at the World Cup for a fourth consecutive appearance, and seventh time overall. They are aiming to get out of the group stage for the first t</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ousmane Dembele News: Scores, assists in victory</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/ousmane-dembele-news-scores-assists-in-victory-520564</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Dembele scored one goal and assisted once from four shots and three chances created in Monday's 3-0 victory over Iraq.
+Dem</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3277,7 +3537,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Is Tunisia's World Cup campaign Africa's worst ever, as Herve Renard magic fails?</t>
+          <t>Tunisia head coach Herve Renard's deal ends after just two FIFA World Cup matches</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3287,70 +3547,97 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-22T09:05:04</t>
+          <t>2026-06-22T21:34:51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.espn.com/espn/story/_/id/49142156/is-tunisia-world-cup-campaign-africa-worst-ever-herve-renard-magic-fails</t>
+          <t>https://www.espn.com/espn/story/_/id/49146731/tunisia-head-coach-herve-renard-deal-ends-just-two-fifa-world-cup-matches</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Herve Renard warned, before taking the reins in his first match as Tunisia coach, against Japan on Saturday, that there were 'no magicians in football</t>
+          <t>Tunisia head coach Herve Renard has confirmed speculation that his contract to oversee the Carthage Eagles only runs until the end of the FIFA World C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Is Tunisia's World Cup campaign Africa's worst ever, as Herve Renard magic fails?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-22T09:05:04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/espn/story/_/id/49142156/is-tunisia-world-cup-campaign-africa-worst-ever-herve-renard-magic-fails</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Herve Renard warned, before taking the reins in his first match as Tunisia coach, against Japan on Saturday, that there were 'no magicians in football</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>武磊：感觉日本队每一个位置都没有短板，整体非常强大</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-06-22 08:32</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956412</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2026美加墨世界杯小组赛第2轮角逐，日本队4-0大胜突尼斯队。上海海港球员武磊在连线节目中表示：“感觉日本队每一个位置都没有短板，整体非常强大。”
 武磊说道：“我觉得现在日本队整体非常强大，每一个位置感觉都比较平均，好像没有哪一个位置稍弱一点。就像刚才说的，前锋位置上，不只是一个得分点，有很多得分</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>日媒：日本队已乘坐包机返回纳什维尔驻地；久保建英依旧单练</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-06-22 07:49</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956353</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>北京时间6月22日，据日本媒体共同通讯社消息，日本队已乘坐包机返回纳什维尔驻地；久保建英依旧单练。
 据报道，世界杯小组赛第二轮，日本国家队4-0大胜突尼斯，球队于当地时间21日搭乘包机从墨西哥蒙特雷返回集训驻地——美国田纳西州纳什维尔。
@@ -3358,28 +3645,28 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>4-0突尼斯，日本终结连续5届世界杯小组赛第二轮不胜魔咒</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2026-06-22 07:41</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956343</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>世界杯小组赛第二轮，日本对阵突尼斯，最终日本国家队4-0大胜突尼斯。
 据统计，日本本轮大胜后终结了连续5届世界杯小组赛第二轮不胜魔咒，自2006年世界杯以来，日本队在世界杯小组赛第二轮未尝胜绩，本届世界杯终于打破魔咒。
@@ -3389,56 +3676,56 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>突尼斯队长：在世界杯提前出局的结果很苦涩；我想向球迷诚挚道歉</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2026-06-22 07:33</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956333</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>在 2026 世界杯小组赛中，突尼斯队在连续输给瑞典和日本之后提前无缘小组出线。作为队长的斯希里在赛后接受FIFA采访时，向球迷表达了诚挚歉意，并直言球队本届赛事的表现远未达到应有水平。
 本届世界杯开始前，突尼斯一度被外界寄予厚望。球队抵达小组赛驻地墨西哥蒙特雷时，普遍被认为有机会冲击队史首次世界</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>镰田大地：上轮那球主要是运气，我不想只留下侥幸破门的印象</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-06-22 07:24</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956314</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>世界杯小组赛第二轮，日本4-0击败突尼斯赛后，日本国脚镰田大地接受了gekisaka的采访。
 “我赛前预判本场控球占优，所以比起参与后场组织，我更想多穿插至门前危险区域。我一直希望能复刻南野拓实的跑动方式，能早早取得进球实在太好了。”
@@ -3446,33 +3733,10 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Depay: No Shots on Target Yet at World Cup 2026, But Praised by the Dutch King</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-06-21T16:38:56</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/depay-no-shots-on-target-yet-at-world-cup-2026-but-praised-by-the-dutch-king</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dutch World Cup Dominance: The Highest Sofascore Ratings in Oranje History</t>
+          <t>Depay: No Shots on Target Yet at World Cup 2026, But Praised by the Dutch King</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3482,74 +3746,74 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-21T12:07:11</t>
+          <t>2026-06-21T16:38:56</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/dutch-world-cup-dominance-the-highest-sofascore-ratings-in-oranje-history</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Cody Gakpo’s 9.7 vs Sweden puts him on the Dutch World Cup all‑time list. He also leads the tournament with an 8.50 average Sofascore Rating.</t>
-        </is>
-      </c>
+          <t>https://www.sofascore.com/news/depay-no-shots-on-target-yet-at-world-cup-2026-but-praised-by-the-dutch-king</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dutch royals enjoy two big results in one World Cup day</t>
+          <t>Dutch World Cup Dominance: The Highest Sofascore Ratings in Oranje History</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-21T09:45:57</t>
+          <t>2026-06-21T12:07:11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c4gydq973nqo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.sofascore.com/news/dutch-world-cup-dominance-the-highest-sofascore-ratings-in-oranje-history</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">King Willem-Alexander celebrated with Curacao's players after they secured their first World Cup point  Two nations, four points, one crazy World Cup </t>
+          <t>Cody Gakpo’s 9.7 vs Sweden puts him on the Dutch World Cup all‑time list. He also leads the tournament with an 8.50 average Sofascore Rating.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>官方：荷兰裁判梅凯利将执法世界杯摩洛哥vs海地</t>
+          <t>Dutch royals enjoy two big results in one World Cup day</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-21 20:53</t>
+          <t>2026-06-21T09:45:57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955288.html</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/c4gydq973nqo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">King Willem-Alexander celebrated with Curacao's players after they secured their first World Cup point  Two nations, four points, one crazy World Cup </t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>荷兰5球大胜瑞典，世界杯连续不败场次超越贝利时代巴西</t>
+          <t>官方：荷兰裁判梅凯利将执法世界杯摩洛哥vs海地</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3559,12 +3823,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-21 20:21</t>
+          <t>2026-06-21 20:53</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955233.html</t>
+          <t>https://www.dongqiudi.com/articles/5955288.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -3572,7 +3836,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>巴萨球员国家队战报：德容首发出场，荷兰大胜</t>
+          <t>荷兰5球大胜瑞典，世界杯连续不败场次超越贝利时代巴西</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3582,12 +3846,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-21 19:20</t>
+          <t>2026-06-21 20:21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955118.html</t>
+          <t>https://www.dongqiudi.com/articles/5955233.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -3595,7 +3859,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>波兰前国脚：看瑞典1-5输荷兰，心想幸好我们没进世界杯</t>
+          <t>巴萨球员国家队战报：德容首发出场，荷兰大胜</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3605,12 +3869,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-21 18:26</t>
+          <t>2026-06-21 19:20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954986.html</t>
+          <t>https://www.dongqiudi.com/articles/5955118.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -3618,7 +3882,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4-0大胜突尼斯，日本是首支在世界杯单场进4球的亚洲球队</t>
+          <t>波兰前国脚：看瑞典1-5输荷兰，心想幸好我们没进世界杯</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3628,12 +3892,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-21 17:34</t>
+          <t>2026-06-21 18:26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954887.html</t>
+          <t>https://www.dongqiudi.com/articles/5954986.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -3641,7 +3905,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>为纪念第一千场世界杯，日本与突尼斯球衣上均印有纪念臂章</t>
+          <t>4-0大胜突尼斯，日本是首支在世界杯单场进4球的亚洲球队</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3651,12 +3915,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-21 15:02</t>
+          <t>2026-06-21 17:34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954627.html</t>
+          <t>https://www.dongqiudi.com/articles/5954887.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -3664,7 +3928,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>两连败狂丢九球，突尼斯成为本届世界杯第三支提前出局的球队</t>
+          <t>为纪念第一千场世界杯，日本与突尼斯球衣上均印有纪念臂章</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3674,12 +3938,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-21 14:14</t>
+          <t>2026-06-21 15:02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954523.html</t>
+          <t>https://www.dongqiudi.com/articles/5954627.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -3687,7 +3951,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TA：荷兰队边路下底进攻套路熟练，他们是世界杯夺冠热门之一</t>
+          <t>两连败狂丢九球，突尼斯成为本届世界杯第三支提前出局的球队</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3697,12 +3961,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-21 07:55</t>
+          <t>2026-06-21 14:14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953878.html</t>
+          <t>https://www.dongqiudi.com/articles/5954523.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -3710,7 +3974,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>波特：荷兰队把球场宽度利用得非常好；我们交了世界杯的学费</t>
+          <t>TA：荷兰队边路下底进攻套路熟练，他们是世界杯夺冠热门之一</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3720,12 +3984,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-21 05:46</t>
+          <t>2026-06-21 07:55</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953597.html</t>
+          <t>https://www.dongqiudi.com/articles/5953878.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -3733,7 +3997,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>邓弗里斯：荷兰有实力赢得世界杯，但必须每场比赛都证明自己</t>
+          <t>波特：荷兰队把球场宽度利用得非常好；我们交了世界杯的学费</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3743,12 +4007,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-21 05:27</t>
+          <t>2026-06-21 05:46</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953634.html</t>
+          <t>https://www.dongqiudi.com/articles/5953597.html</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -3756,61 +4020,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
+          <t>邓弗里斯：荷兰有实力赢得世界杯，但必须每场比赛都证明自己</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-20T23:46:26</t>
+          <t>2026-06-21 05:27</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953634.html</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Netherlands crush Sweden with dominant World Cup display in Houston</t>
+          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-20T21:08:11</t>
+          <t>2026-06-20T23:46:26</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/netherlands-crush-sweden-with-dominant-world-cup-display-in-houston</t>
+          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Netherlands crushed Sweden 5-1 in World Cup Group F. Cody Gakpo scored twice, assisted once, and earned a 9.7 Sofascore Rating in a clinical team disp</t>
+          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Netherlands vs Sweden: World Cup Group F pregame at NRG Stadium</t>
+          <t>Netherlands crush Sweden with dominant World Cup display in Houston</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3820,51 +4080,51 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-20T10:00:00</t>
+          <t>2026-06-20T21:08:11</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/netherlands-vs-sweden-world-cup-group-f-pregame-at-nrg-stadium</t>
+          <t>https://www.sofascore.com/news/netherlands-crush-sweden-with-dominant-world-cup-display-in-houston</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Group F heads to Houston as the Netherlands meet Sweden. We break down form, key stats, head-to-head, players to watch, and the latest odds for this W</t>
+          <t>Netherlands crushed Sweden 5-1 in World Cup Group F. Cody Gakpo scored twice, assisted once, and earned a 9.7 Sofascore Rating in a clinical team disp</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tunisia vs Japan Prediction: World Cup 2026 Match Preview</t>
+          <t>Netherlands vs Sweden: World Cup Group F pregame at NRG Stadium</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-19T12:05:35</t>
+          <t>2026-06-20T10:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/tunisia-vs-japan-prediction-world-cup-2026-match-preview/</t>
+          <t>https://www.sofascore.com/news/netherlands-vs-sweden-world-cup-group-f-pregame-at-nrg-stadium</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Can Hervé Renard spark a Tunisian revival in the tournament’s 1,000 th match? Look ahead to this Group F match at the 2026 FIFA World Cup with our Tun</t>
+          <t>Group F heads to Houston as the Netherlands meet Sweden. We break down form, key stats, head-to-head, players to watch, and the latest odds for this W</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Netherlands vs Sweden Prediction: World Cup 2026 Match Preview</t>
+          <t>Tunisia vs Japan Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3874,102 +4134,106 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-19T11:39:07</t>
+          <t>2026-06-19T12:05:35</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/netherlands-vs-sweden-prediction-world-cup-2026-match-preview/</t>
+          <t>https://theanalyst.com/articles/tunisia-vs-japan-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>After drawing their opening game, can the Oranje pick up their first victory against a Swedish side sitting pretty at the top of Group F at the 2026 F</t>
+          <t>Can Hervé Renard spark a Tunisian revival in the tournament’s 1,000 th match? Look ahead to this Group F match at the 2026 FIFA World Cup with our Tun</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Netherlands vs Sweden Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-19T11:39:07</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/netherlands-vs-sweden-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>After drawing their opening game, can the Oranje pick up their first victory against a Swedish side sitting pretty at the top of Group F at the 2026 F</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>World Cup 2026 Group F: Latest table, fixtures and results</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>1 day ago</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-group-f-latest-table-fixtures-and-results/</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t xml:space="preserve">Group F at World Cup 2026 looks to be one that has the potential for the biggest shock.
 The draw placed Netherlands into Group F alongside Japan and </t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Tunisia World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>squawka</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1 day ago</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://www.squawka.com/en/news/world-cup/tunisia-world-cup-2026-fixtures-results-squad-analysis/</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Tunisia have never reached the knockout stages of the World Cup and will miss out yet again. They’ve bowed out at the group stage in each of their sev</t>
-        </is>
-      </c>
-    </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>武磊：加克波能传能射、能带来多样性变化，很好的团队型球员</t>
+          <t>Tunisia World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>squawka</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-22 14:47</t>
+          <t>1 day ago</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956987.html</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>https://www.squawka.com/en/news/world-cup/tunisia-world-cup-2026-fixtures-results-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Tunisia have never reached the knockout stages of the World Cup and will miss out yet again. They’ve bowed out at the group stage in each of their sev</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>利物浦球员国家队战报：加克波两射一传，伊萨克送助攻</t>
+          <t>武磊：加克波能传能射、能带来多样性变化，很好的团队型球员</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3979,12 +4243,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-21 19:56</t>
+          <t>2026-06-22 14:47</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955188.html</t>
+          <t>https://www.dongqiudi.com/articles/5956987.html</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -3992,18 +4256,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>利物浦找到了激活加克波的秘诀！</t>
+          <t>利物浦球员国家队战报：加克波两射一传，伊萨克送助攻</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-21 19:56</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://n.dongqiudi.com/webapp/top.html?articleId=5957125&amp;from=tab_253</t>
+          <t>https://www.dongqiudi.com/articles/5955188.html</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -4011,34 +4279,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>How to watch New Zealand vs Egypt for FREE: Live stream details for World Cup 2026</t>
+          <t>利物浦找到了激活加克波的秘诀！</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 23</t>
-        </is>
-      </c>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/competition/watch-new-zealand-vs-egypt-free-world-cup-2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>After the first round of World Cup 2026 matches, Group G couldn't be more finely balanced with all four teams on one point.  New Zealand vs Egypt, the</t>
-        </is>
-      </c>
+          <t>https://n.dongqiudi.com/webapp/top.html?articleId=5957125&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>How to watch Spain vs Saudi Arabia for FREE: Live stream details as European champions aim to kickstart their World Cup 2026</t>
+          <t>How to watch New Zealand vs Egypt for FREE: Live stream details for World Cup 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4048,149 +4308,228 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 14</t>
+          <t>Sun, 21 Jun 2026 23</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/competition/watch-spain-vs-saudi-arabia-free-world-cup-2026</t>
+          <t>https://www.fourfourtwo.com/competition/watch-new-zealand-vs-egypt-free-world-cup-2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spain take on Saudi Arabia in a World Cup 2026 Group H game from Atlanta that has more riding on it than many predicted when the draw was first made. </t>
+          <t>After the first round of World Cup 2026 matches, Group G couldn't be more finely balanced with all four teams on one point.  New Zealand vs Egypt, the</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>How to watch Spain vs Saudi Arabia for FREE: Live stream details as European champions aim to kickstart their World Cup 2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 14</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/watch-spain-vs-saudi-arabia-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spain take on Saudi Arabia in a World Cup 2026 Group H game from Atlanta that has more riding on it than many predicted when the draw was first made. </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>How Deniz Undav became Germany’s World Cup 2026 supersub</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/person/player/how-deniz-undav-became-germanys-world-cup-2026-supersub</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denis Undav turns 30 on Sunday, July 19. A significant date for another reason – it's is the date of the 2026 World Cup Final which will be played at </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Japan outclass Tunisia 4-0 in Group F: Ueda shines</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-06-21T08:06:08</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/japan-outclass-tunisia-4-0-in-group-f-ueda-shines</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Tunisia vs Japan: Group F pregame at Estadio BBVA</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-06-20T15:00:00</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/tunisia-vs-japan-group-f-pregame-at-estadio-bbva</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Tunisia face Japan in World Cup Group F at Estadio BBVA. See odds in decimal, H2H record, likely lineups, and Players to watch with Sofascore Rating.</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>World Cup 2026: Routes to the final</t>
+          <t>Japan outclass Tunisia 4-0 in Group F: Ueda shines</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-06-19T12:00:00</t>
+          <t>2026-06-21T08:06:08</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
-        </is>
-      </c>
+          <t>https://www.sofascore.com/news/japan-outclass-tunisia-4-0-in-group-f-ueda-shines</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Tunisia vs Japan: Group F pregame at Estadio BBVA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-06-20T15:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/tunisia-vs-japan-group-f-pregame-at-estadio-bbva</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Tunisia face Japan in World Cup Group F at Estadio BBVA. See odds in decimal, H2H record, likely lineups, and Players to watch with Sofascore Rating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>World Cup 2026: Routes to the final</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fifa</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-06-19T12:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>Iran World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>11 hours ago</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/iran-world-cup-2026-fixtures-squad-analysis-june-21/</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Iran are at the World Cup for a fourth consecutive appearance, and seventh time overall. They are aiming to get out of the group stage for the first t</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ousmane Dembele News: Scores, assists in victory</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/ousmane-dembele-news-scores-assists-in-victory-520564</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Dembele scored one goal and assisted once from four shots and three chances created in Monday's 3-0 victory over Iraq.
+Dem</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4243,7 +4582,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>How to watch Uruguay vs Cape Verde for FREE: Live stream details for World Cup 2026</t>
+          <t>How to watch Jordan vs Algeria for FREE: Live stream details for World Cup 2026 clash</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4253,56 +4592,56 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 20</t>
+          <t>Tue, 23 Jun 2026 01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/competition/watch-uruguay-vs-cape-verde-free-world-cup-2026</t>
+          <t>https://www.fourfourtwo.com/competition/watch-jordan-vs-algeria-for-free-world-cup-2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Few would have predicted before the World Cup 2026 that Group H would be this tight after the opening round of fixtures, but with all four teams on on</t>
+          <t>Jordan and Algeria each fell to defeats in their opening Group J fixtures of World Cup 2026 and both sides know that another loss would virtually spel</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans</t>
+          <t>How to watch Uruguay vs Cape Verde for FREE: Live stream details for World Cup 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>skysports</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 15</t>
+          <t>Sun, 21 Jun 2026 20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/football/live-blog/12040/13509050/world-cup-2026-news-and-live-updates-usa-canada-and-mexico-latest-including-trump-tickets-and-fans</t>
+          <t>https://www.fourfourtwo.com/competition/watch-uruguay-vs-cape-verde-free-world-cup-2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Update World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans Sunday 21 June 2026 15:14, UK Sorry, thi</t>
+          <t>Few would have predicted before the World Cup 2026 that Group H would be this tight after the opening round of fixtures, but with all four teams on on</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>How to watch Belgium vs Iran for FREE: Live stream details as Red Devils attempt to crack open Group G at World Cup 2026</t>
+          <t>World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>skysports</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4312,46 +4651,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/competition/how-to-watch-belgium-vs-iran-for-free</t>
+          <t>https://www.skysports.com/football/live-blog/12040/13509050/world-cup-2026-news-and-live-updates-usa-canada-and-mexico-latest-including-trump-tickets-and-fans</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Belgium and Iran might not have willingly accepted draws in their first matches at World Cup 2026 but the state of Group G after 90 minutes suggests t</t>
+          <t>Update World Cup 2026 news and live updates - USA, Canada and Mexico latest including Trump, tickets and fans Sunday 21 June 2026 15:14, UK Sorry, thi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+          <t>How to watch Belgium vs Iran for FREE: Live stream details as Red Devils attempt to crack open Group G at World Cup 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 13</t>
+          <t>Sun, 21 Jun 2026 15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
+          <t>https://www.fourfourtwo.com/competition/how-to-watch-belgium-vs-iran-for-free</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
+          <t>Belgium and Iran might not have willingly accepted draws in their first matches at World Cup 2026 but the state of Group G after 90 minutes suggests t</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4361,24 +4700,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 09</t>
+          <t>Sun, 21 Jun 2026 13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Australia’s Jackson Irvine has no sympathy for Paraguay after historic World Cup red card</t>
+          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4388,216 +4727,228 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 04</t>
+          <t>Sun, 21 Jun 2026 09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/australias-jackson-irvine-has-no-sympathy-for-paraguay-after-historic-world-cup-red-card</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Miguel Almirón sent off against Turkey for covering mouth  Socceroos face South Americans in crucial last Group D match  Socceroo Jackson Irvine has b</t>
+          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>How to watch Ecuador vs Curacao for FREE: Live stream details as both sides look for a response in World Cup 2026 Group E</t>
+          <t>Australia’s Jackson Irvine has no sympathy for Paraguay after historic World Cup red card</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 22</t>
+          <t>Sun, 21 Jun 2026 04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/competition/watch-ecuador-vs-curacao-free-world-cup-2026</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/australias-jackson-irvine-has-no-sympathy-for-paraguay-after-historic-world-cup-red-card</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ecuador vs Curacao at the World Cup 2026 could scarcely have more riding on it.  Both sides lost their Group E openers and know another defeat would a</t>
+          <t>Miguel Almirón sent off against Turkey for covering mouth  Socceroos face South Americans in crucial last Group D match  Socceroo Jackson Irvine has b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>‘Everybody’s crying’: Turkey crash out as 10-man Paraguay hang on for World Cup win</t>
+          <t>How to watch Ecuador vs Curacao for FREE: Live stream details as both sides look for a response in World Cup 2026 Group E</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 07</t>
+          <t>Sat, 20 Jun 2026 22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/20/turkey-paraguay-world-cup-2026-group-d-match-report</t>
+          <t>https://www.fourfourtwo.com/competition/watch-ecuador-vs-curacao-free-world-cup-2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Turkey arrived at their first World Cup in 24 years with great expectations and a host of rising stars but crashed ⁠out goalless and in tears ⁠after a</t>
+          <t>Ecuador vs Curacao at the World Cup 2026 could scarcely have more riding on it.  Both sides lost their Group E openers and know another defeat would a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>How far can the USA go at the 2026 World Cup? Hugely favourable route to semi-finals revealed</t>
+          <t>‘Everybody’s crying’: Turkey crash out as 10-man Paraguay hang on for World Cup win</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 08</t>
+          <t>Sat, 20 Jun 2026 07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/team/how-far-can-the-usa-go-at-the-2026-world-cup-hugely-favourable-route-to-semi-finals-revealed</t>
+          <t>https://www.theguardian.com/football/2026/jun/20/turkey-paraguay-world-cup-2026-group-d-match-report</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">As the group stage of the 2026 FIFA World Cup nears its conclusion, the United States Men’s National Team (USMNT) have positioned themselves strongly </t>
+          <t>Turkey arrived at their first World Cup in 24 years with great expectations and a host of rising stars but crashed ⁠out goalless and in tears ⁠after a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>USMNT faces World Cup dilemma vs. Turkiye: Rotate squad or keep same XI?</t>
+          <t>USMNT’s Alex Zendejas, yet to play at World Cup, readies for his moment: ‘I’m sure it’ll come’</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-22T07:13:47</t>
+          <t>Mon, 22 Jun 2026 21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49140112/usmnt-faces-world-cup-dilemma-vs-turkiye-rotate-squad-keep-same-xi</t>
+          <t>https://www.theguardian.com/football/2026/jun/22/usmnt-alex-zendejas-world-cup</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The USMNT has clinched a spot in the World Cup knockouts, so should the team rotate in its final Group D match or stay consistent?</t>
+          <t xml:space="preserve">Club América star did not appear in first two US games  Dual-national was surprise pick to Pochettino’s squad  Dead-rubber Turkey match could be time </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>外媒：世界杯球场外盗版球衣40美元一件，美国球迷不爱买伊朗球衣</t>
+          <t>How far can the USA go at the 2026 World Cup? Hugely favourable route to semi-finals revealed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zhibo8</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-22 17:50:15</t>
+          <t>Mon, 22 Jun 2026 08</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a3902e6349f3native.htm</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>https://www.fourfourtwo.com/team/how-far-can-the-usa-go-at-the-2026-world-cup-hugely-favourable-route-to-semi-finals-revealed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As the group stage of the 2026 FIFA World Cup nears its conclusion, the United States Men’s National Team (USMNT) have positioned themselves strongly </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>弗里曼：在世界杯为美国队进球，对我和家人而言是一个圆满时刻</t>
+          <t>Balogun admits eyeing up Donovan's USMNT World Cup goals record</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-21 01:01</t>
+          <t>2026-06-22T18:14:12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953156.html</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>https://www.espn.com/video/clip/_/id/49145542/balogun-admits-eyeing-donovan-usmnt-world-cup-goals-record</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Balogun admits eyeing up Donovan's USMNT World Cup goals record</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>没用的纪录+1，土耳其后卫巴尔达克奇98传0失误创世界杯纪录</t>
+          <t>USMNT faces World Cup dilemma vs. Turkiye: Rotate squad or keep same XI?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-20 23:44</t>
+          <t>2026-06-22T07:13:47</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953015.html</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49140112/usmnt-faces-world-cup-dilemma-vs-turkiye-rotate-squad-keep-same-xi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>The USMNT has clinched a spot in the World Cup knockouts, so should the team rotate in its final Group D match or stay consistent?</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>伊布：美国队能拿下本届世界杯冠军</t>
+          <t>外媒：世界杯球场外盗版球衣40美元一件，美国球迷不爱买伊朗球衣</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>zhibo8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-20 21:51</t>
+          <t>2026-06-22 17:50:15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5952703.html</t>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a3902e6349f3native.htm</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -4605,7 +4956,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>美国队后卫弗里曼：世界杯两连胜后，球队的信心已经非常强了</t>
+          <t>弗里曼：在世界杯为美国队进球，对我和家人而言是一个圆满时刻</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4615,12 +4966,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-20 07:58</t>
+          <t>2026-06-21 01:01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5950946.html</t>
+          <t>https://www.dongqiudi.com/articles/5953156.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -4628,217 +4979,286 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>USA 2-0 Australia at HT: World Cup Group D report</t>
+          <t>没用的纪录+1，土耳其后卫巴尔达克奇98传0失误创世界杯纪录</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-19T22:00:50</t>
+          <t>2026-06-20 23:44</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/usa-2-0-australia-at-ht-world-cup-group-d-report</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>USA control Australia 2-0 at halftime in World Cup Group D. Freeman’s goal and a Burgess own goal headline a half driven by 70% possession and 1.17 xG</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953015.html</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Türkiye vs Paraguay Prediction: World Cup 2026 Match Preview</t>
+          <t>伊布：美国队能拿下本届世界杯冠军</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-19T21:55:43</t>
+          <t>2026-06-20 21:51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/turkiye-vs-paraguay-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Both beaten in their opening 2026 FIFA World Cup fixture, Group D’s bottom two face a crucial clash in San Francisco. We look ahead to Friday’s game w</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5952703.html</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>美国队后卫弗里曼：世界杯两连胜后，球队的信心已经非常强了</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-20 07:58</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5950946.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>USA 2-0 Australia at HT: World Cup Group D report</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:00:50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/usa-2-0-australia-at-ht-world-cup-group-d-report</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>USA control Australia 2-0 at halftime in World Cup Group D. Freeman’s goal and a Burgess own goal headline a half driven by 70% possession and 1.17 xG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Türkiye vs Paraguay Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-19T21:55:43</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/turkiye-vs-paraguay-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Both beaten in their opening 2026 FIFA World Cup fixture, Group D’s bottom two face a crucial clash in San Francisco. We look ahead to Friday’s game w</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>USA 2-0 Australia Stats: Co-Hosts Through to Knockouts Another Dominant World Cup Win</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2026-06-19T21:28:10</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/usa-vs-australia-stats-world-cup-2026-live/</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>USA confirmed their qualification for the knockout stages of their home World Cup after a thoroughly deserved win over Australia.
 The United States b</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>USA vs Australia Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2026-06-19T07:58:23</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/usa-vs-australia-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>After both sides earned impressive victories in their opening matches, who can seize the initiative and take charge of Group D? We look ahead to Frida</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Paraguay vs Australia FIFA World Cup 2026 Preview: Everything you need to know</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2026-06-21T11:19:49</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/paraguay-australia-world-cup-preview/blt9c01b7bae1a3bfbd</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>GOAL brings you everything you need to know about Paraguay vs Australia at the 2026 FIFA World Cup.
 Paraguay vs Australia will kick-off on 26 June 20</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Ten-man Paraguay hold firm to defeat Türkiye in crucial Group D clash</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2026-06-20T07:13:25</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/ten-man-paraguay-hold-firm-to-defeat-turkiye-in-crucial-group-d-clash</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Paraguay struck early through Matías Galarza, then defended superbly after Miguel Almirón’s red card. Juan Cáceres earned an 8.2 Sofascore Rating in a</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>USA vs Australia pregame: what to expect in Group D</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>2026-06-19T10:00:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/usa-vs-australia-pregame-what-to-expect-in-group-d</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>USA face Australia in World Cup Group D at Lumen Field. Form trends, H2H, team news, decimal odds, and Sofascore Rating standouts set the scene.</t>
         </is>
@@ -4855,7 +5275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4975,118 +5395,130 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>How far can the USA go at the 2026 World Cup? Hugely favourable route to semi-finals revealed</t>
+          <t>USMNT’s Alex Zendejas, yet to play at World Cup, readies for his moment: ‘I’m sure it’ll come’</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fourfourtwo</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 08</t>
+          <t>Mon, 22 Jun 2026 21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/team/how-far-can-the-usa-go-at-the-2026-world-cup-hugely-favourable-route-to-semi-finals-revealed</t>
+          <t>https://www.theguardian.com/football/2026/jun/22/usmnt-alex-zendejas-world-cup</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">As the group stage of the 2026 FIFA World Cup nears its conclusion, the United States Men’s National Team (USMNT) have positioned themselves strongly </t>
+          <t xml:space="preserve">Club América star did not appear in first two US games  Dual-national was surprise pick to Pochettino’s squad  Dead-rubber Turkey match could be time </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Socceroos World Cup Daily: Socceroos are walking the tightrope</t>
+          <t>How to watch France vs Iraq for FREE: Live stream details as Kylian Mbappe chases history at World Cup 2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-22T07:08:00</t>
+          <t>Mon, 22 Jun 2026 19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48811876/socceroos-world-cup-daily-news-updates-all-need-know</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>https://www.fourfourtwo.com/competition/watch-france-vs-iraq-for-free-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kylian Mbappe broke France's goalscoring record, on matchday one at the World Cup 2026 , and Les Bleus' skipper will be hungry for more as he leads hi</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>法媒：巴黎球探考察世界杯，对澳大利亚中卫奇尔卡蒂印象深刻</t>
+          <t>How far can the USA go at the 2026 World Cup? Hugely favourable route to semi-finals revealed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-22 05:03</t>
+          <t>Mon, 22 Jun 2026 08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956110.html</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>https://www.fourfourtwo.com/team/how-far-can-the-usa-go-at-the-2026-world-cup-hugely-favourable-route-to-semi-finals-revealed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As the group stage of the 2026 FIFA World Cup nears its conclusion, the United States Men’s National Team (USMNT) have positioned themselves strongly </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>世界杯首轮速度榜：澳大利亚后卫力压哈兰德居首，姆巴佩第9</t>
+          <t>Inside the Socceroos' plans to make history in the World Cup knockouts</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-21 09:10</t>
+          <t>2026-06-22T21:57:40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5954018.html</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49147185/inside-australia-socceroos-plans-make-history-world-cup-knockouts-paraguay-group-d</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hayden Foxe has tells ESPN extensive work has been done to ensure the Socceroos will be ready to pursue a first-ever knockout stage win regardless of </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>世界杯史上最早的“绝杀”，巴拉圭队加拉尔萨65秒攻入制胜球</t>
+          <t>Socceroos World Cup Daily: Socceroos are walking the tightrope</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-21 00:12</t>
+          <t>2026-06-22T07:08:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953092.html</t>
+          <t>https://www.espn.com/soccer/story/_/id/48811876/socceroos-world-cup-daily-news-updates-all-need-know</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -5094,389 +5526,458 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Juan Cáceres shines as Paraguay knock Türkiye out of the World Cup</t>
+          <t>法媒：巴黎球探考察世界杯，对澳大利亚中卫奇尔卡蒂印象深刻</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-20T07:20:55</t>
+          <t>2026-06-22 05:03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/juan-caceres-shines-as-paraguay-knock-turkiye-out-of-the-world-cup</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Paraguay beat Türkiye 1-0 in Santa Clara, and Juan Cáceres stood out at right back with 17 duels won, 9 tackles, 6 clearances and perfect long passing</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5956110.html</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>世界杯首轮速度榜：澳大利亚后卫力压哈兰德居首，姆巴佩第9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-21 09:10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5954018.html</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>世界杯史上最早的“绝杀”，巴拉圭队加拉尔萨65秒攻入制胜球</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-21 00:12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5953092.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Juan Cáceres shines as Paraguay knock Türkiye out of the World Cup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-20T07:20:55</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/juan-caceres-shines-as-paraguay-knock-turkiye-out-of-the-world-cup</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Paraguay beat Türkiye 1-0 in Santa Clara, and Juan Cáceres stood out at right back with 17 duels won, 9 tackles, 6 clearances and perfect long passing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>The best photos from Matchday 9</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-06-20T05:00:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/best-photos-matchday-9</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Enjoy an array of the best photos from the most recent round of fixtures at the FIFA World Cup 2026.
 Two USA fans dressed as bald eagles pose ahead o</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>巴拉圭主帅：等待16年重返世界杯，我们从第一分钟就开始战斗</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-06-20 16:05</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5951773.html</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>澳大利亚队在世界杯总共已打进3粒乌龙球，并列历史第二多</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-06-20 09:18</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5951068.html</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>USA 2-0 Australia at HT: World Cup Group D report</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-06-19T22:00:50</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/usa-2-0-australia-at-ht-world-cup-group-d-report</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>USA control Australia 2-0 at halftime in World Cup Group D. Freeman’s goal and a Burgess own goal headline a half driven by 70% possession and 1.17 xG</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Türkiye vs Paraguay Prediction: World Cup 2026 Match Preview</t>
+          <t>巴拉圭主帅：等待16年重返世界杯，我们从第一分钟就开始战斗</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-19T21:55:43</t>
+          <t>2026-06-20 16:05</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/turkiye-vs-paraguay-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Both beaten in their opening 2026 FIFA World Cup fixture, Group D’s bottom two face a crucial clash in San Francisco. We look ahead to Friday’s game w</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5951773.html</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>澳大利亚队在世界杯总共已打进3粒乌龙球，并列历史第二多</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-20 09:18</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951068.html</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>USA 2-0 Australia at HT: World Cup Group D report</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-19T22:00:50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/usa-2-0-australia-at-ht-world-cup-group-d-report</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>USA control Australia 2-0 at halftime in World Cup Group D. Freeman’s goal and a Burgess own goal headline a half driven by 70% possession and 1.17 xG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Türkiye vs Paraguay Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-19T21:55:43</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/turkiye-vs-paraguay-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Both beaten in their opening 2026 FIFA World Cup fixture, Group D’s bottom two face a crucial clash in San Francisco. We look ahead to Friday’s game w</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>USA 2-0 Australia Stats: Co-Hosts Through to Knockouts Another Dominant World Cup Win</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>2026-06-19T21:28:10</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/usa-vs-australia-stats-world-cup-2026-live/</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>USA confirmed their qualification for the knockout stages of their home World Cup after a thoroughly deserved win over Australia.
 The United States b</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Türkiye vs Paraguay: preview from Santa Clara</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>2026-06-19T15:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/turkiye-vs-paraguay-preview-from-santa-clara</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Türkiye face Paraguay in World Cup 2026 Group D at Levi’s Stadium. We break down form, streaks, odds in decimal, and the key Sofascore Rating standout</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>USA vs Australia Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2026-06-19T07:58:23</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/usa-vs-australia-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>After both sides earned impressive victories in their opening matches, who can seize the initiative and take charge of Group D? We look ahead to Frida</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Gustavo Caballero Injury: Still training individually</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>rotowire</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://www.rotowire.com/soccer/headlines/gustavo-caballero-injury-still-training-individually-520477</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Written by RotoWire Staff
 Caballero (strain) continues to train individually with Paraguay, with his availability for Thursday's clash against Austra</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Ramon Sosa Injury: Trains individually Sunday</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>rotowire</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://www.rotowire.com/soccer/headlines/ramon-sosa-injury-trains-individually-sunday-520476</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Written by RotoWire Staff
 Sosa (ankle) was training individually with Paraguay on Sunday, raising some uncertainty over his availability for Thursday</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Diego Gomez News: Trains in full, not injured</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>rotowire</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://www.rotowire.com/soccer/headlines/diego-gomez-news-trains-in-full-not-injured-520475</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Written by RotoWire Staff
 Gomez trained fully with the Paraguay squad on Sunday, confirming his recovery from the minor knee discomfort that forced h</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Ten-man Paraguay hold firm to defeat Türkiye in crucial Group D clash</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2026-06-20T07:13:25</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/ten-man-paraguay-hold-firm-to-defeat-turkiye-in-crucial-group-d-clash</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Paraguay struck early through Matías Galarza, then defended superbly after Miguel Almirón’s red card. Juan Cáceres earned an 8.2 Sofascore Rating in a</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>USA vs Australia pregame: what to expect in Group D</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>2026-06-19T10:00:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/usa-vs-australia-pregame-what-to-expect-in-group-d</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>USA face Australia in World Cup Group D at Lumen Field. Form trends, H2H, team news, decimal odds, and Sofascore Rating standouts set the scene.</t>
         </is>
